--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.90296450515828</v>
+        <v>14.88016484227437</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.95957620211899</v>
+        <v>15.93456464640785</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.31804695971721</v>
+        <v>13.29856513607414</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38251.8116821659</v>
+        <v>38532.41951675555</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.545527744733976</v>
+        <v>1.556865435020427</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>618.4133333333335</v>
+        <v>617.3903607047478</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>652.7466666666669</v>
+        <v>651.7236940380811</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.95957620211899</v>
+        <v>15.93456464640785</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.95957620211899</v>
+        <v>15.93456464640785</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.74290953545232</v>
+        <v>13.71827148671962</v>
       </c>
       <c r="F11" t="n">
-        <v>10.86680779054871</v>
+        <v>10.84732596690564</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.31804695971721</v>
+        <v>13.29856513607414</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.44886888220132</v>
+        <v>11.43062915189419</v>
       </c>
       <c r="C2" t="n">
-        <v>12.87427241286233</v>
+        <v>12.85375271626681</v>
       </c>
       <c r="D2" t="n">
-        <v>14.29967594352334</v>
+        <v>14.27687628063942</v>
       </c>
       <c r="E2" t="n">
-        <v>15.72507947418434</v>
+        <v>15.69999984501203</v>
       </c>
       <c r="F2" t="n">
-        <v>17.15048300484535</v>
+        <v>17.12312340938465</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.75051316301879</v>
+        <v>11.73227343271166</v>
       </c>
       <c r="C3" t="n">
-        <v>13.1759166936798</v>
+        <v>13.15539699708428</v>
       </c>
       <c r="D3" t="n">
-        <v>14.60132022434081</v>
+        <v>14.57852056145689</v>
       </c>
       <c r="E3" t="n">
-        <v>16.02672375500181</v>
+        <v>16.0016441258295</v>
       </c>
       <c r="F3" t="n">
-        <v>17.45212728566282</v>
+        <v>17.42476769020212</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.05215744383626</v>
+        <v>12.03391771352913</v>
       </c>
       <c r="C4" t="n">
-        <v>13.47756097449727</v>
+        <v>13.45704127790175</v>
       </c>
       <c r="D4" t="n">
-        <v>14.90296450515828</v>
+        <v>14.88016484227437</v>
       </c>
       <c r="E4" t="n">
-        <v>16.32836803581928</v>
+        <v>16.30328840664697</v>
       </c>
       <c r="F4" t="n">
-        <v>17.7537715664803</v>
+        <v>17.72641197101959</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.35380172465374</v>
+        <v>12.3355619943466</v>
       </c>
       <c r="C5" t="n">
-        <v>13.77920525531474</v>
+        <v>13.75868555871922</v>
       </c>
       <c r="D5" t="n">
-        <v>15.20460878597575</v>
+        <v>15.18180912309184</v>
       </c>
       <c r="E5" t="n">
-        <v>16.63001231663675</v>
+        <v>16.60493268746445</v>
       </c>
       <c r="F5" t="n">
-        <v>18.05541584729777</v>
+        <v>18.02805625183706</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.65544600547121</v>
+        <v>12.63720627516408</v>
       </c>
       <c r="C6" t="n">
-        <v>14.08084953613221</v>
+        <v>14.06032983953669</v>
       </c>
       <c r="D6" t="n">
-        <v>15.50625306679322</v>
+        <v>15.48345340390931</v>
       </c>
       <c r="E6" t="n">
-        <v>16.93165659745423</v>
+        <v>16.90657696828192</v>
       </c>
       <c r="F6" t="n">
-        <v>18.35706012811524</v>
+        <v>18.32970053265453</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.1</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.39</v>
+        <v>15.37</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38532.41951675555</v>
+        <v>43824.66306824519</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.556865435020427</v>
+        <v>1.770693457302836</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.43</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43824.66306824519</v>
+        <v>49486.13291402483</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.770693457302836</v>
+        <v>1.999439713697973</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.89</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49486.13291402483</v>
+        <v>43209.28591109523</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.999439713697973</v>
+        <v>1.745829733781626</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.38</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43209.28591109523</v>
+        <v>51701.4906797647</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.745829733781626</v>
+        <v>2.088949118374331</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.88016484227437</v>
+        <v>15.08798757794616</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.29856513607414</v>
+        <v>13.81812197525362</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51701.4906797647</v>
+        <v>41676.49060351594</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.088949118374331</v>
+        <v>1.683898610243068</v>
       </c>
     </row>
   </sheetData>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.71827148671962</v>
+        <v>14.37533865648951</v>
       </c>
       <c r="F11" t="n">
-        <v>10.84732596690564</v>
+        <v>11.36688280608512</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.29856513607414</v>
+        <v>13.81812197525362</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.43062915189419</v>
+        <v>11.41684169818692</v>
       </c>
       <c r="C2" t="n">
-        <v>12.85375271626681</v>
+        <v>12.81769835285226</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27687628063942</v>
+        <v>14.2185550075176</v>
       </c>
       <c r="E2" t="n">
-        <v>15.69999984501203</v>
+        <v>15.61941166218293</v>
       </c>
       <c r="F2" t="n">
-        <v>17.12312340938465</v>
+        <v>17.02026831684827</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.73227343271166</v>
+        <v>11.8515579834012</v>
       </c>
       <c r="C3" t="n">
-        <v>13.15539699708428</v>
+        <v>13.25241463806654</v>
       </c>
       <c r="D3" t="n">
-        <v>14.57852056145689</v>
+        <v>14.65327129273188</v>
       </c>
       <c r="E3" t="n">
-        <v>16.0016441258295</v>
+        <v>16.05412794739721</v>
       </c>
       <c r="F3" t="n">
-        <v>17.42476769020212</v>
+        <v>17.45498460206255</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.03391771352913</v>
+        <v>12.28627426861549</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45704127790175</v>
+        <v>13.68713092328082</v>
       </c>
       <c r="D4" t="n">
-        <v>14.88016484227437</v>
+        <v>15.08798757794616</v>
       </c>
       <c r="E4" t="n">
-        <v>16.30328840664697</v>
+        <v>16.48884423261149</v>
       </c>
       <c r="F4" t="n">
-        <v>17.72641197101959</v>
+        <v>17.88970088727683</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.3355619943466</v>
+        <v>12.72099055382977</v>
       </c>
       <c r="C5" t="n">
-        <v>13.75868555871922</v>
+        <v>14.1218472084951</v>
       </c>
       <c r="D5" t="n">
-        <v>15.18180912309184</v>
+        <v>15.52270386316044</v>
       </c>
       <c r="E5" t="n">
-        <v>16.60493268746445</v>
+        <v>16.92356051782577</v>
       </c>
       <c r="F5" t="n">
-        <v>18.02805625183706</v>
+        <v>18.32441717249111</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.63720627516408</v>
+        <v>13.15570683904405</v>
       </c>
       <c r="C6" t="n">
-        <v>14.06032983953669</v>
+        <v>14.55656349370938</v>
       </c>
       <c r="D6" t="n">
-        <v>15.48345340390931</v>
+        <v>15.95742014837472</v>
       </c>
       <c r="E6" t="n">
-        <v>16.90657696828192</v>
+        <v>17.35827680304005</v>
       </c>
       <c r="F6" t="n">
-        <v>18.32970053265453</v>
+        <v>18.75913345770539</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.08</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.3</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.37</v>
+        <v>15.15</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.07</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>41676.49060351594</v>
+        <v>25023.38777247853</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.683898610243068</v>
+        <v>1.011045970605193</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25023.38777247853</v>
+        <v>32538.63417828004</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.011045970605193</v>
+        <v>1.314692290031517</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1250,35 +1249,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.08798757794616</v>
+        <v>16.75238338175389</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.93456464640785</v>
+        <v>17.7950797229573</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.81812197525362</v>
+        <v>15.18833886994876</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32538.63417828004</v>
+        <v>18010.34170400495</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.314692290031517</v>
+        <v>0.7276905738991897</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>617.3903607047478</v>
+        <v>580.6367236850256</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.2</v>
+        <v>47.214</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131</v>
+        <v>119.684</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-103.4</v>
+        <v>-103.359</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.8</v>
+        <v>-1.746</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-88.8</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>651.7236940380811</v>
+        <v>727.0630570183589</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40900000</v>
+        <v>40857533</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.93456464640785</v>
+        <v>17.7950797229573</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.93456464640785</v>
+        <v>17.7950797229573</v>
       </c>
     </row>
     <row r="14">
@@ -822,13 +822,13 @@
         <v>22000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4651362420843521</v>
+        <v>0.4352501465886352</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3102458734702628</v>
+        <v>0.2903118477746197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3022562354849589</v>
+        <v>0.2828355627861388</v>
       </c>
     </row>
     <row r="3">
@@ -844,13 +844,13 @@
         <v>30000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8313545746026895</v>
+        <v>0.7843920294331035</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5545135012599939</v>
+        <v>0.52318948363188</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5263209234736367</v>
+        <v>0.4965894816828201</v>
       </c>
     </row>
     <row r="4">
@@ -866,13 +866,13 @@
         <v>28000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7397999914731052</v>
+        <v>0.6971065587219865</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4934465943125612</v>
+        <v>0.464970074667565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4562973239814467</v>
+        <v>0.4299646673979741</v>
       </c>
     </row>
     <row r="5">
@@ -888,13 +888,13 @@
         <v>19000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3278043673899756</v>
+        <v>0.3043219405219595</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2186455130491137</v>
+        <v>0.202982734328147</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1969779396838862</v>
+        <v>0.1828673282235559</v>
       </c>
     </row>
     <row r="6">
@@ -910,13 +910,13 @@
         <v>18000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2820270758251833</v>
+        <v>0.260679205166401</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1881120595753973</v>
+        <v>0.1738730298459895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1651060224205514</v>
+        <v>0.1526084209001756</v>
       </c>
     </row>
     <row r="7">
@@ -932,13 +932,13 @@
         <v>23000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5109135336491443</v>
+        <v>0.4788928819441937</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3407793269439792</v>
+        <v>0.3194215522567772</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2913994801405701</v>
+        <v>0.2731365048109862</v>
       </c>
     </row>
     <row r="8">
@@ -954,13 +954,13 @@
         <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6482454083435208</v>
+        <v>0.6098210880108693</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4323796873651284</v>
+        <v>0.4067506657032499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3602052764683161</v>
+        <v>0.3388543455548256</v>
       </c>
     </row>
     <row r="9">
@@ -976,13 +976,13 @@
         <v>18000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2820270758251833</v>
+        <v>0.260679205166401</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1881120595753973</v>
+        <v>0.1738730298459895</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1526759675151345</v>
+        <v>0.1411192515591181</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.451239169168501</v>
+        <v>2.297975562915594</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.37533865648951</v>
+        <v>16.30203646021475</v>
       </c>
       <c r="F11" t="n">
-        <v>11.36688280608512</v>
+        <v>12.89036330703316</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.81812197525362</v>
+        <v>15.18833886994876</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.41684169818692</v>
+        <v>13.27394221969284</v>
       </c>
       <c r="C2" t="n">
-        <v>12.81769835285226</v>
+        <v>14.59871696651525</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2185550075176</v>
+        <v>15.92349171333766</v>
       </c>
       <c r="E2" t="n">
-        <v>15.61941166218293</v>
+        <v>17.24826646016006</v>
       </c>
       <c r="F2" t="n">
-        <v>17.02026831684827</v>
+        <v>18.57304120698247</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.8515579834012</v>
+        <v>13.68838805390095</v>
       </c>
       <c r="C3" t="n">
-        <v>13.25241463806654</v>
+        <v>15.01316280072336</v>
       </c>
       <c r="D3" t="n">
-        <v>14.65327129273188</v>
+        <v>16.33793754754577</v>
       </c>
       <c r="E3" t="n">
-        <v>16.05412794739721</v>
+        <v>17.66271229436818</v>
       </c>
       <c r="F3" t="n">
-        <v>17.45498460206255</v>
+        <v>18.98748704119059</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.28627426861549</v>
+        <v>14.10283388810907</v>
       </c>
       <c r="C4" t="n">
-        <v>13.68713092328082</v>
+        <v>15.42760863493147</v>
       </c>
       <c r="D4" t="n">
-        <v>15.08798757794616</v>
+        <v>16.75238338175389</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48884423261149</v>
+        <v>18.07715812857629</v>
       </c>
       <c r="F4" t="n">
-        <v>17.88970088727683</v>
+        <v>19.4019328753987</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.72099055382977</v>
+        <v>14.51727972231718</v>
       </c>
       <c r="C5" t="n">
-        <v>14.1218472084951</v>
+        <v>15.84205446913959</v>
       </c>
       <c r="D5" t="n">
-        <v>15.52270386316044</v>
+        <v>17.166829215962</v>
       </c>
       <c r="E5" t="n">
-        <v>16.92356051782577</v>
+        <v>18.4916039627844</v>
       </c>
       <c r="F5" t="n">
-        <v>18.32441717249111</v>
+        <v>19.81637870960682</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.15570683904405</v>
+        <v>14.93172555652529</v>
       </c>
       <c r="C6" t="n">
-        <v>14.55656349370938</v>
+        <v>16.2565003033477</v>
       </c>
       <c r="D6" t="n">
-        <v>15.95742014837472</v>
+        <v>17.58127505017011</v>
       </c>
       <c r="E6" t="n">
-        <v>17.35827680304005</v>
+        <v>18.90604979699252</v>
       </c>
       <c r="F6" t="n">
-        <v>18.75913345770539</v>
+        <v>20.23082454381493</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.11</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.15</v>
+        <v>16.81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18010.34170400495</v>
+        <v>1481.079857180723</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7276905738991897</v>
+        <v>0.05984161039114032</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.25</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1481.079857180723</v>
+        <v>7407.42747318052</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05984161039114032</v>
+        <v>0.2992899989163846</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.86</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7407.42747318052</v>
+        <v>11814.83791587424</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2992899989163846</v>
+        <v>0.4773671885201715</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.32</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11814.83791587424</v>
+        <v>21503.86216070459</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4773671885201715</v>
+        <v>0.868842915584024</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.39</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21503.86216070459</v>
+        <v>16487.14339721867</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.868842915584024</v>
+        <v>0.666147207968431</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.83</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16487.14339721867</v>
+        <v>19622.73576094323</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.666147207968431</v>
+        <v>0.7928378085229588</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.18</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19622.73576094323</v>
+        <v>12560.35186148972</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7928378085229588</v>
+        <v>0.5074889641005949</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.75238338175389</v>
+        <v>16.77122513321292</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.7950797229573</v>
+        <v>17.81584308197886</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.18833886994876</v>
+        <v>15.204298210064</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12560.35186148972</v>
+        <v>12384.76700558313</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5074889641005949</v>
+        <v>0.5003946264882075</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>580.6367236850256</v>
+        <v>581.4850633114395</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>727.0630570183589</v>
+        <v>727.9113966447729</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.7950797229573</v>
+        <v>17.81584308197886</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.7950797229573</v>
+        <v>17.81584308197886</v>
       </c>
     </row>
     <row r="14">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16.30203646021475</v>
+        <v>16.32221973497922</v>
       </c>
       <c r="F11" t="n">
-        <v>12.89036330703316</v>
+        <v>12.90632264714841</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.18833886994876</v>
+        <v>15.204298210064</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.27394221969284</v>
+        <v>13.28901562086006</v>
       </c>
       <c r="C2" t="n">
-        <v>14.59871696651525</v>
+        <v>14.61567454282838</v>
       </c>
       <c r="D2" t="n">
-        <v>15.92349171333766</v>
+        <v>15.94233346479669</v>
       </c>
       <c r="E2" t="n">
-        <v>17.24826646016006</v>
+        <v>17.268992386765</v>
       </c>
       <c r="F2" t="n">
-        <v>18.57304120698247</v>
+        <v>18.59565130873331</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.68838805390095</v>
+        <v>13.70346145506818</v>
       </c>
       <c r="C3" t="n">
-        <v>15.01316280072336</v>
+        <v>15.03012037703649</v>
       </c>
       <c r="D3" t="n">
-        <v>16.33793754754577</v>
+        <v>16.3567792990048</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66271229436818</v>
+        <v>17.68343822097312</v>
       </c>
       <c r="F3" t="n">
-        <v>18.98748704119059</v>
+        <v>19.01009714294143</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.10283388810907</v>
+        <v>14.11790728927629</v>
       </c>
       <c r="C4" t="n">
-        <v>15.42760863493147</v>
+        <v>15.44456621124461</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75238338175389</v>
+        <v>16.77122513321292</v>
       </c>
       <c r="E4" t="n">
-        <v>18.07715812857629</v>
+        <v>18.09788405518123</v>
       </c>
       <c r="F4" t="n">
-        <v>19.4019328753987</v>
+        <v>19.42454297714954</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.51727972231718</v>
+        <v>14.53235312348441</v>
       </c>
       <c r="C5" t="n">
-        <v>15.84205446913959</v>
+        <v>15.85901204545272</v>
       </c>
       <c r="D5" t="n">
-        <v>17.166829215962</v>
+        <v>17.18567096742103</v>
       </c>
       <c r="E5" t="n">
-        <v>18.4916039627844</v>
+        <v>18.51232988938935</v>
       </c>
       <c r="F5" t="n">
-        <v>19.81637870960682</v>
+        <v>19.83898881135766</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.93172555652529</v>
+        <v>14.94679895769252</v>
       </c>
       <c r="C6" t="n">
-        <v>16.2565003033477</v>
+        <v>16.27345787966083</v>
       </c>
       <c r="D6" t="n">
-        <v>17.58127505017011</v>
+        <v>17.60011680162914</v>
       </c>
       <c r="E6" t="n">
-        <v>18.90604979699252</v>
+        <v>18.92677572359746</v>
       </c>
       <c r="F6" t="n">
-        <v>20.23082454381493</v>
+        <v>20.25343464556577</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.77</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.81</v>
+        <v>16.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.4</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12384.76700558313</v>
+        <v>16226.79670586264</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5003946264882075</v>
+        <v>0.6556281497318239</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.82</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16226.79670586264</v>
+        <v>23305.78640765781</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6556281497318239</v>
+        <v>0.9416479356629417</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.61</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23305.78640765781</v>
+        <v>30382.40476866478</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9416479356629417</v>
+        <v>1.227571909845042</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.4</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30382.40476866478</v>
+        <v>24201.56088373464</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.227571909845042</v>
+        <v>0.9778408437872583</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.77122513321292</v>
+        <v>17.13246874501721</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.81584308197886</v>
+        <v>17.37335263085518</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.204298210064</v>
+        <v>16.77114291626024</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24201.56088373464</v>
+        <v>21596.79778295173</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9778408437872583</v>
+        <v>0.8725978902202718</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>581.4850633114395</v>
+        <v>572.4978649978361</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49.13333333333333</v>
+        <v>181.8600781420178</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.214</v>
+        <v>48.138</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119.684</v>
+        <v>125.818</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-103.359</v>
+        <v>-33.381</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.746</v>
+        <v>-1.599</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>-183.6</v>
       </c>
     </row>
     <row r="9">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>727.9113966447729</v>
+        <v>709.733943139854</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40857533</v>
+        <v>40851870</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.81584308197886</v>
+        <v>17.37335263085518</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.81584308197886</v>
+        <v>17.37335263085518</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -822,13 +822,13 @@
         <v>22000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4352501465886352</v>
+        <v>0.6273651372017977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2903118477746197</v>
+        <v>0.418452546513599</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2828355627861388</v>
+        <v>0.4076763053237459</v>
       </c>
     </row>
     <row r="3">
@@ -844,13 +844,13 @@
         <v>30000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7843920294331035</v>
+        <v>1.046393475439435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.52318948363188</v>
+        <v>0.6979444481181034</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4965894816828201</v>
+        <v>0.6624595535223631</v>
       </c>
     </row>
     <row r="4">
@@ -866,13 +866,13 @@
         <v>28000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6971065587219865</v>
+        <v>0.9416363908800258</v>
       </c>
       <c r="E4" t="n">
-        <v>0.464970074667565</v>
+        <v>0.6280714727169773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4299646673979741</v>
+        <v>0.5807869292706305</v>
       </c>
     </row>
     <row r="5">
@@ -888,13 +888,13 @@
         <v>19000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3043219405219595</v>
+        <v>0.4702295103626835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.202982734328147</v>
+        <v>0.3136430834119099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1828673282235559</v>
+        <v>0.2825613364071261</v>
       </c>
     </row>
     <row r="6">
@@ -910,13 +910,13 @@
         <v>18000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.260679205166401</v>
+        <v>0.4178509680829788</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1738730298459895</v>
+        <v>0.2787065957113469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1526084209001756</v>
+        <v>0.244620879406349</v>
       </c>
     </row>
     <row r="7">
@@ -932,13 +932,13 @@
         <v>23000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4788928819441937</v>
+        <v>0.6797436794815023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3194215522567772</v>
+        <v>0.453389034214162</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2731365048109862</v>
+        <v>0.3876917360458335</v>
       </c>
     </row>
     <row r="8">
@@ -954,13 +954,13 @@
         <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6098210880108693</v>
+        <v>0.8368793063206164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4067506657032499</v>
+        <v>0.5581984973158511</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3388543455548256</v>
+        <v>0.4650219469724118</v>
       </c>
     </row>
     <row r="9">
@@ -976,13 +976,13 @@
         <v>18000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.260679205166401</v>
+        <v>0.4178509680829788</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1738730298459895</v>
+        <v>0.2787065957113469</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1411192515591181</v>
+        <v>0.2262045253724104</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.297975562915594</v>
+        <v>3.25702321232087</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16.32221973497922</v>
+        <v>17.09088152861629</v>
       </c>
       <c r="F11" t="n">
-        <v>12.90632264714841</v>
+        <v>13.51411970393937</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.204298210064</v>
+        <v>16.77114291626024</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.28901562086006</v>
+        <v>12.88609922381494</v>
       </c>
       <c r="C2" t="n">
-        <v>14.61567454282838</v>
+        <v>14.51188004140332</v>
       </c>
       <c r="D2" t="n">
-        <v>15.94233346479669</v>
+        <v>16.13766085899169</v>
       </c>
       <c r="E2" t="n">
-        <v>17.268992386765</v>
+        <v>17.76344167658007</v>
       </c>
       <c r="F2" t="n">
-        <v>18.59565130873331</v>
+        <v>19.38922249416843</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.70346145506818</v>
+        <v>13.3835031668277</v>
       </c>
       <c r="C3" t="n">
-        <v>15.03012037703649</v>
+        <v>15.00928398441608</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3567792990048</v>
+        <v>16.63506480200445</v>
       </c>
       <c r="E3" t="n">
-        <v>17.68343822097312</v>
+        <v>18.26084561959282</v>
       </c>
       <c r="F3" t="n">
-        <v>19.01009714294143</v>
+        <v>19.88662643718119</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.11790728927629</v>
+        <v>13.88090710984046</v>
       </c>
       <c r="C4" t="n">
-        <v>15.44456621124461</v>
+        <v>15.50668792742884</v>
       </c>
       <c r="D4" t="n">
-        <v>16.77122513321292</v>
+        <v>17.13246874501721</v>
       </c>
       <c r="E4" t="n">
-        <v>18.09788405518123</v>
+        <v>18.75824956260558</v>
       </c>
       <c r="F4" t="n">
-        <v>19.42454297714954</v>
+        <v>20.38403038019394</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.53235312348441</v>
+        <v>14.37831105285322</v>
       </c>
       <c r="C5" t="n">
-        <v>15.85901204545272</v>
+        <v>16.0040918704416</v>
       </c>
       <c r="D5" t="n">
-        <v>17.18567096742103</v>
+        <v>17.62987268802997</v>
       </c>
       <c r="E5" t="n">
-        <v>18.51232988938935</v>
+        <v>19.25565350561834</v>
       </c>
       <c r="F5" t="n">
-        <v>19.83898881135766</v>
+        <v>20.8814343232067</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.94679895769252</v>
+        <v>14.87571499586598</v>
       </c>
       <c r="C6" t="n">
-        <v>16.27345787966083</v>
+        <v>16.50149581345435</v>
       </c>
       <c r="D6" t="n">
-        <v>17.60011680162914</v>
+        <v>18.12727663104273</v>
       </c>
       <c r="E6" t="n">
-        <v>18.92677572359746</v>
+        <v>19.7530574486311</v>
       </c>
       <c r="F6" t="n">
-        <v>20.25343464556577</v>
+        <v>21.37883826621946</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.79</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.82</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.83</v>
+        <v>17.21</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.13246874501721</v>
+        <v>17.22201436034435</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.77114291626024</v>
+        <v>16.86889172915243</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22000</v>
+        <v>29250</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.375</v>
+        <v>1.676805005952179</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21596.79778295173</v>
+        <v>22102.24246494873</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8725978902202718</v>
+        <v>0.8118116395766954</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +773,7 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="C2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6273651372017977</v>
+        <v>0.8984240934992694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.418452546513599</v>
+        <v>0.5992488703640128</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4076763053237459</v>
+        <v>0.583816653703862</v>
       </c>
     </row>
     <row r="3">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="C3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="D3" t="n">
-        <v>1.046393475439435</v>
+        <v>0.8984240934992694</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6979444481181034</v>
+        <v>0.5992488703640128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6624595535223631</v>
+        <v>0.5687818567516555</v>
       </c>
     </row>
     <row r="4">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="C4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9416363908800258</v>
+        <v>0.8958051663852842</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6280714727169773</v>
+        <v>0.5975020459789846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5807869292706305</v>
+        <v>0.5525189307132071</v>
       </c>
     </row>
     <row r="5">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="C5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4702295103626835</v>
+        <v>0.8958051663852842</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3136430834119099</v>
+        <v>0.5975020459789846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2825613364071261</v>
+        <v>0.5382901315125986</v>
       </c>
     </row>
     <row r="6">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4178509680829788</v>
+        <v>0.689564656158947</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2787065957113469</v>
+        <v>0.4599396256580177</v>
       </c>
       <c r="F6" t="n">
-        <v>0.244620879406349</v>
+        <v>0.4036891750449185</v>
       </c>
     </row>
     <row r="7">
@@ -926,19 +926,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6797436794815023</v>
+        <v>0.689564656158947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.453389034214162</v>
+        <v>0.4599396256580177</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3876917360458335</v>
+        <v>0.3932931290601069</v>
       </c>
     </row>
     <row r="8">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8368793063206164</v>
+        <v>0.689564656158947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5581984973158511</v>
+        <v>0.4599396256580177</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4650219469724118</v>
+        <v>0.3831648082926146</v>
       </c>
     </row>
     <row r="9">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4178509680829788</v>
+        <v>0.689564656158947</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2787065957113469</v>
+        <v>0.4599396256580177</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2262045253724104</v>
+        <v>0.37329731812192</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.25702321232087</v>
+        <v>3.796852003200883</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.09088152861629</v>
+        <v>16.53179690486822</v>
       </c>
       <c r="F11" t="n">
-        <v>13.51411970393937</v>
+        <v>13.07203972595154</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.77114291626024</v>
+        <v>16.86889172915243</v>
       </c>
     </row>
     <row r="13">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
   </sheetData>
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.88609922381494</v>
+        <v>13.08471432485743</v>
       </c>
       <c r="C2" t="n">
-        <v>14.51188004140332</v>
+        <v>14.74525114219415</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13766085899169</v>
+        <v>16.40578795953086</v>
       </c>
       <c r="E2" t="n">
-        <v>17.76344167658007</v>
+        <v>18.06632477686758</v>
       </c>
       <c r="F2" t="n">
-        <v>19.38922249416843</v>
+        <v>19.72686159420428</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.3835031668277</v>
+        <v>13.49282752526418</v>
       </c>
       <c r="C3" t="n">
-        <v>15.00928398441608</v>
+        <v>15.1533643426009</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63506480200445</v>
+        <v>16.81390115993761</v>
       </c>
       <c r="E3" t="n">
-        <v>18.26084561959282</v>
+        <v>18.47443797727433</v>
       </c>
       <c r="F3" t="n">
-        <v>19.88662643718119</v>
+        <v>20.13497479461103</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.88090710984046</v>
+        <v>13.90094072567092</v>
       </c>
       <c r="C4" t="n">
-        <v>15.50668792742884</v>
+        <v>15.56147754300764</v>
       </c>
       <c r="D4" t="n">
-        <v>17.13246874501721</v>
+        <v>17.22201436034435</v>
       </c>
       <c r="E4" t="n">
-        <v>18.75824956260558</v>
+        <v>18.88255117768107</v>
       </c>
       <c r="F4" t="n">
-        <v>20.38403038019394</v>
+        <v>20.54308799501778</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.37831105285322</v>
+        <v>14.30905392607767</v>
       </c>
       <c r="C5" t="n">
-        <v>16.0040918704416</v>
+        <v>15.96959074341439</v>
       </c>
       <c r="D5" t="n">
-        <v>17.62987268802997</v>
+        <v>17.63012756075111</v>
       </c>
       <c r="E5" t="n">
-        <v>19.25565350561834</v>
+        <v>19.29066437808783</v>
       </c>
       <c r="F5" t="n">
-        <v>20.8814343232067</v>
+        <v>20.95120119542453</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.87571499586598</v>
+        <v>14.71716712648442</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50149581345435</v>
+        <v>16.37770394382114</v>
       </c>
       <c r="D6" t="n">
-        <v>18.12727663104273</v>
+        <v>18.03824076115785</v>
       </c>
       <c r="E6" t="n">
-        <v>19.7530574486311</v>
+        <v>19.69877757849457</v>
       </c>
       <c r="F6" t="n">
-        <v>21.37883826621946</v>
+        <v>21.35931439583128</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>17.16</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>17.2</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>17.21</v>
+        <v>17.29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22102.24246494873</v>
+        <v>21701.97372580275</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8118116395766954</v>
+        <v>0.7971098362681528</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.67</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21701.97372580275</v>
+        <v>31108.28909573347</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7971098362681528</v>
+        <v>1.142602214018912</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.61</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31108.28909573347</v>
+        <v>34910.84211762037</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.142602214018912</v>
+        <v>1.28226934545007</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/asc_fv_report.xlsx
+++ b/outputs/asc_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.99</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34910.84211762037</v>
+        <v>28606.60947607103</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.28226934545007</v>
+        <v>1.050715943340518</v>
       </c>
     </row>
   </sheetData>
